--- a/Excel/WingConfig.xlsx
+++ b/Excel/WingConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>

--- a/Excel/WingConfig.xlsx
+++ b/Excel/WingConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="59">
   <si>
     <t>ID</t>
   </si>
@@ -195,6 +195,15 @@
   </si>
   <si>
     <t>0,0,3000,10,10,10,5,5,1,1</t>
+  </si>
+  <si>
+    <t>6,29,15,2003,2002,2001,2010,2011,32,31,2012</t>
+  </si>
+  <si>
+    <t>400,400,100500,455,405,355,205,155,21,11,1</t>
+  </si>
+  <si>
+    <t>0,0,4000,15,20,10,5,5,1,1,1</t>
   </si>
 </sst>
 </file>
@@ -1163,9 +1172,9 @@
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32.1666666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.3333333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="23.5" style="2" customWidth="1"/>
     <col min="9" max="9" width="11.375" style="2" customWidth="1"/>
     <col min="10" max="10" width="13.25" style="2" customWidth="1"/>
     <col min="11" max="11" width="9.625" style="2" customWidth="1"/>
@@ -2010,7 +2019,32 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1"/>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1">
+        <v>101</v>
+      </c>
+      <c r="E34" s="1">
+        <v>120</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I34" s="1">
+        <v>465</v>
+      </c>
+      <c r="J34" s="1">
+        <v>5</v>
+      </c>
+    </row>
     <row r="35" s="1" customFormat="1" customHeight="1"/>
     <row r="36" s="1" customFormat="1" customHeight="1"/>
     <row r="37" s="1" customFormat="1" customHeight="1"/>

--- a/Excel/WingConfig.xlsx
+++ b/Excel/WingConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="62">
   <si>
     <t>ID</t>
   </si>
@@ -200,10 +200,19 @@
     <t>6,29,15,2003,2002,2001,2010,2011,32,31,2012</t>
   </si>
   <si>
-    <t>400,400,100500,455,405,355,205,155,21,11,1</t>
-  </si>
-  <si>
-    <t>0,0,4000,15,20,10,5,5,1,1,1</t>
+    <t>400,400,100500,455,405,355,205,155,21,11,10</t>
+  </si>
+  <si>
+    <t>0,0,4000,15,20,10,5,5,1,1,10</t>
+  </si>
+  <si>
+    <t>6,29,15,2003,2002,2001,2010,2011,32,31,2012,2004,2005,2006</t>
+  </si>
+  <si>
+    <t>400,400,180500,755,805,555,305,255,41,31,200,10,10,10</t>
+  </si>
+  <si>
+    <t>0,0,5000,30,40,20,10,0,1,1,20,10,10,10</t>
   </si>
 </sst>
 </file>
@@ -1172,9 +1181,9 @@
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32.1666666666667" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.3333333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="43.9166666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="42.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="29.1666666666667" style="2" customWidth="1"/>
     <col min="9" max="9" width="11.375" style="2" customWidth="1"/>
     <col min="10" max="10" width="13.25" style="2" customWidth="1"/>
     <col min="11" max="11" width="9.625" style="2" customWidth="1"/>
@@ -2045,7 +2054,32 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" customHeight="1"/>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C35" s="1">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1">
+        <v>121</v>
+      </c>
+      <c r="E35" s="1">
+        <v>150</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I35" s="1">
+        <v>515</v>
+      </c>
+      <c r="J35" s="1">
+        <v>5</v>
+      </c>
+    </row>
     <row r="36" s="1" customFormat="1" customHeight="1"/>
     <row r="37" s="1" customFormat="1" customHeight="1"/>
     <row r="38" s="1" customFormat="1" customHeight="1"/>

--- a/Excel/WingConfig.xlsx
+++ b/Excel/WingConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="65">
   <si>
     <t>ID</t>
   </si>
@@ -213,6 +213,15 @@
   </si>
   <si>
     <t>0,0,5000,30,40,20,10,0,1,1,20,10,10,10</t>
+  </si>
+  <si>
+    <t>6,29,15,2003,2002,2001,2010,2011,32,31,2012,2004,2005,2006,2013</t>
+  </si>
+  <si>
+    <t>400,400,180500,755,805,555,305,255,41,31,200,10,10,10,20</t>
+  </si>
+  <si>
+    <t>0,0,10000,60,60,40,20,0,1,1,40,20,20,20,20</t>
   </si>
 </sst>
 </file>
@@ -1181,7 +1190,7 @@
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="43.9166666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="47.6666666666667" style="2" customWidth="1"/>
     <col min="7" max="7" width="42.25" style="2" customWidth="1"/>
     <col min="8" max="8" width="29.1666666666667" style="2" customWidth="1"/>
     <col min="9" max="9" width="11.375" style="2" customWidth="1"/>
@@ -1298,7 +1307,7 @@
       </c>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1324,7 +1333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1350,7 +1359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1376,7 +1385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1402,7 +1411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1428,7 +1437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1454,7 +1463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1480,7 +1489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1506,7 +1515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1532,7 +1541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1558,7 +1567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2048,6 +2057,7 @@
         <v>58</v>
       </c>
       <c r="I34" s="1">
+        <f t="shared" ref="I34:I36" si="0">I33+(E33-D33+1)*5</f>
         <v>465</v>
       </c>
       <c r="J34" s="1">
@@ -2074,13 +2084,40 @@
         <v>61</v>
       </c>
       <c r="I35" s="1">
-        <v>515</v>
+        <f t="shared" si="0"/>
+        <v>565</v>
       </c>
       <c r="J35" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1"/>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1">
+        <v>151</v>
+      </c>
+      <c r="E36" s="1">
+        <v>180</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I36" s="1">
+        <f t="shared" si="0"/>
+        <v>715</v>
+      </c>
+      <c r="J36" s="1">
+        <v>5</v>
+      </c>
+    </row>
     <row r="37" s="1" customFormat="1" customHeight="1"/>
     <row r="38" s="1" customFormat="1" customHeight="1"/>
     <row r="39" s="1" customFormat="1" customHeight="1"/>

--- a/Excel/WingConfig.xlsx
+++ b/Excel/WingConfig.xlsx
@@ -218,7 +218,7 @@
     <t>6,29,15,2003,2002,2001,2010,2011,32,31,2012,2004,2005,2006,2013</t>
   </si>
   <si>
-    <t>400,400,180500,755,805,555,305,255,41,31,200,10,10,10,20</t>
+    <t>400,400,335500,1685,2025,1175,615,255,71,61,820,320,320,320,20</t>
   </si>
   <si>
     <t>0,0,10000,60,60,40,20,0,1,1,40,20,20,20,20</t>

--- a/Excel/WingConfig.xlsx
+++ b/Excel/WingConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -2099,7 +2104,7 @@
         <v>151</v>
       </c>
       <c r="E36" s="1">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>62</v>

--- a/Excel/WingConfig.xlsx
+++ b/Excel/WingConfig.xlsx
@@ -2104,7 +2104,7 @@
         <v>151</v>
       </c>
       <c r="E36" s="1">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>62</v>
